--- a/data/grafik-sanrazryva-2026-11.xlsx
+++ b/data/grafik-sanrazryva-2026-11.xlsx
@@ -1839,25 +1839,29 @@
       <c r="I23" s="4" t="n"/>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="O23" s="6" t="inlineStr">
+      <c r="N23" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="Q23" s="4" t="inlineStr">
@@ -1867,35 +1871,31 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ГГ/СО</t>
         </is>
       </c>
       <c r="T23" s="4" t="inlineStr">
         <is>
-          <t>ГФ\СО</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="inlineStr">
-        <is>
           <t>ГФ/ОД</t>
         </is>
       </c>
-      <c r="V23" s="4" t="n"/>
-      <c r="W23" s="7" t="inlineStr">
+      <c r="U23" s="4" t="n"/>
+      <c r="V23" s="7" t="inlineStr">
         <is>
           <t>ПДГ</t>
         </is>
       </c>
-      <c r="X23" s="8" t="inlineStr">
+      <c r="W23" s="8" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="X23" s="4" t="n"/>
       <c r="Y23" s="4" t="n"/>
       <c r="Z23" s="4" t="n"/>
       <c r="AA23" s="4" t="n"/>
@@ -1928,63 +1928,63 @@
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="O24" s="6" t="inlineStr">
+      <c r="P24" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
-      <c r="P24" s="4" t="inlineStr">
+      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>ПР/Р</t>
         </is>
       </c>
-      <c r="Q24" s="4" t="inlineStr">
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
         </is>
       </c>
-      <c r="R24" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
-      <c r="S24" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ГГ</t>
-        </is>
-      </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>ГФ\СО</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr">
         <is>
+          <t>ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
           <t>ГФ/ОД</t>
         </is>
       </c>
-      <c r="V24" s="4" t="n"/>
-      <c r="W24" s="7" t="inlineStr">
+      <c r="W24" s="4" t="n"/>
+      <c r="X24" s="7" t="inlineStr">
         <is>
           <t>ПДГ</t>
         </is>
       </c>
-      <c r="X24" s="8" t="inlineStr">
+      <c r="Y24" s="8" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n"/>
       <c r="AA24" s="4" t="n"/>
       <c r="AB24" s="4" t="n"/>
@@ -2035,22 +2035,22 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
           <t>Р\ДС</t>
         </is>
       </c>
-      <c r="S25" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
       <c r="T25" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="U25" s="4" t="inlineStr">
         <is>
-          <t>ГФ\СО</t>
+          <t>ДЗ/ГГ/СО</t>
         </is>
       </c>
       <c r="V25" s="4" t="inlineStr">
@@ -2119,22 +2119,22 @@
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="S26" s="4" t="inlineStr">
+        <is>
           <t>Р\ДС</t>
         </is>
       </c>
-      <c r="S26" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
         <is>
-          <t>ГФ\СО</t>
+          <t>ДЗ/ГГ/СО</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr">
@@ -2203,22 +2203,22 @@
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="S27" s="4" t="inlineStr">
+        <is>
           <t>Р\ДС</t>
         </is>
       </c>
-      <c r="S27" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
       <c r="T27" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="U27" s="4" t="inlineStr">
         <is>
-          <t>ГФ\СО</t>
+          <t>ДЗ/ГГ/СО</t>
         </is>
       </c>
       <c r="V27" s="4" t="inlineStr">
@@ -2287,22 +2287,22 @@
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
           <t>Р\ДС</t>
         </is>
       </c>
-      <c r="S28" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="U28" s="4" t="inlineStr">
         <is>
-          <t>ГФ\СО</t>
+          <t>ДЗ/ГГ/СО</t>
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr">
@@ -2349,25 +2349,29 @@
       <c r="K29" s="4" t="n"/>
       <c r="L29" s="4" t="n"/>
       <c r="M29" s="4" t="n"/>
-      <c r="N29" s="4" t="n"/>
-      <c r="O29" s="5" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="P29" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="S29" s="4" t="inlineStr">
@@ -2377,35 +2381,31 @@
       </c>
       <c r="T29" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="U29" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ГГ/СО</t>
         </is>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>ГФ\СО</t>
-        </is>
-      </c>
-      <c r="W29" s="4" t="inlineStr">
-        <is>
           <t>ГФ/ОД</t>
         </is>
       </c>
-      <c r="X29" s="4" t="n"/>
-      <c r="Y29" s="7" t="inlineStr">
+      <c r="W29" s="4" t="n"/>
+      <c r="X29" s="7" t="inlineStr">
         <is>
           <t>ПДГ</t>
         </is>
       </c>
-      <c r="Z29" s="8" t="inlineStr">
+      <c r="Y29" s="8" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="Z29" s="4" t="n"/>
       <c r="AA29" s="4" t="n"/>
       <c r="AB29" s="4" t="n"/>
       <c r="AC29" s="4" t="n"/>
@@ -2433,25 +2433,29 @@
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="5" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="P30" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="S30" s="4" t="inlineStr">
@@ -2461,35 +2465,31 @@
       </c>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ГГ/СО</t>
         </is>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>ГФ\СО</t>
-        </is>
-      </c>
-      <c r="W30" s="4" t="inlineStr">
-        <is>
           <t>ГФ/ОД</t>
         </is>
       </c>
-      <c r="X30" s="4" t="n"/>
-      <c r="Y30" s="7" t="inlineStr">
+      <c r="W30" s="4" t="n"/>
+      <c r="X30" s="7" t="inlineStr">
         <is>
           <t>ПДГ</t>
         </is>
       </c>
-      <c r="Z30" s="8" t="inlineStr">
+      <c r="Y30" s="8" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="Z30" s="4" t="n"/>
       <c r="AA30" s="4" t="n"/>
       <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="4" t="n"/>
@@ -2517,25 +2517,29 @@
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
-      <c r="O31" s="5" t="inlineStr">
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="P31" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="P31" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="S31" s="4" t="inlineStr">
@@ -2545,35 +2549,31 @@
       </c>
       <c r="T31" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="U31" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ГГ/СО</t>
         </is>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>ГФ\СО</t>
-        </is>
-      </c>
-      <c r="W31" s="4" t="inlineStr">
-        <is>
           <t>ГФ/ОД</t>
         </is>
       </c>
-      <c r="X31" s="4" t="n"/>
-      <c r="Y31" s="7" t="inlineStr">
+      <c r="W31" s="4" t="n"/>
+      <c r="X31" s="7" t="inlineStr">
         <is>
           <t>ПДГ</t>
         </is>
       </c>
-      <c r="Z31" s="8" t="inlineStr">
+      <c r="Y31" s="8" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="Z31" s="4" t="n"/>
       <c r="AA31" s="4" t="n"/>
       <c r="AB31" s="4" t="n"/>
       <c r="AC31" s="4" t="n"/>
@@ -2601,25 +2601,29 @@
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
-      <c r="O32" s="5" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="P32" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="S32" s="4" t="inlineStr">
@@ -2629,35 +2633,31 @@
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ГГ/СО</t>
         </is>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>ГФ\СО</t>
-        </is>
-      </c>
-      <c r="W32" s="4" t="inlineStr">
-        <is>
           <t>ГФ/ОД</t>
         </is>
       </c>
-      <c r="X32" s="4" t="n"/>
-      <c r="Y32" s="7" t="inlineStr">
+      <c r="W32" s="4" t="n"/>
+      <c r="X32" s="7" t="inlineStr">
         <is>
           <t>ПДГ</t>
         </is>
       </c>
-      <c r="Z32" s="8" t="inlineStr">
+      <c r="Y32" s="8" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="Z32" s="4" t="n"/>
       <c r="AA32" s="4" t="n"/>
       <c r="AB32" s="4" t="n"/>
       <c r="AC32" s="4" t="n"/>
@@ -2690,63 +2690,67 @@
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="4" t="n"/>
       <c r="N33" s="4" t="n"/>
-      <c r="O33" s="4" t="n"/>
-      <c r="P33" s="5" t="inlineStr">
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="Q33" s="4" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="T33" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="U33" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗОН</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="X33" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="Y33" s="4" t="n"/>
-      <c r="Z33" s="7" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AA33" s="8" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="Y33" s="7" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="Z33" s="8" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AA33" s="4" t="n"/>
       <c r="AB33" s="4" t="n"/>
       <c r="AC33" s="4" t="n"/>
       <c r="AD33" s="4" t="n"/>
@@ -2778,63 +2782,67 @@
       <c r="L34" s="4" t="n"/>
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
-      <c r="O34" s="4" t="n"/>
-      <c r="P34" s="5" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="U34" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗОН</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="X34" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="Y34" s="4" t="n"/>
-      <c r="Z34" s="7" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AA34" s="8" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="Y34" s="7" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="Z34" s="8" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AA34" s="4" t="n"/>
       <c r="AB34" s="4" t="n"/>
       <c r="AC34" s="4" t="n"/>
       <c r="AD34" s="4" t="n"/>
@@ -2862,63 +2870,67 @@
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
       <c r="N35" s="4" t="n"/>
-      <c r="O35" s="4" t="n"/>
-      <c r="P35" s="5" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="Q35" s="4" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="R35" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="T35" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="U35" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗОН</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="X35" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="Y35" s="4" t="n"/>
-      <c r="Z35" s="7" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AA35" s="8" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="Y35" s="7" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="Z35" s="8" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AA35" s="4" t="n"/>
       <c r="AB35" s="4" t="n"/>
       <c r="AC35" s="4" t="n"/>
       <c r="AD35" s="4" t="n"/>
@@ -2946,63 +2958,67 @@
       <c r="L36" s="4" t="n"/>
       <c r="M36" s="4" t="n"/>
       <c r="N36" s="4" t="n"/>
-      <c r="O36" s="4" t="n"/>
-      <c r="P36" s="5" t="inlineStr">
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="Q36" s="4" t="inlineStr">
+      <c r="P36" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="U36" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗОН</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="X36" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="Y36" s="4" t="n"/>
-      <c r="Z36" s="7" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AA36" s="8" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="Y36" s="7" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="Z36" s="8" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AA36" s="4" t="n"/>
       <c r="AB36" s="4" t="n"/>
       <c r="AC36" s="4" t="n"/>
       <c r="AD36" s="4" t="n"/>
@@ -3031,63 +3047,67 @@
       <c r="M37" s="4" t="n"/>
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
-      <c r="P37" s="4" t="n"/>
-      <c r="Q37" s="5" t="inlineStr">
+      <c r="P37" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="R37" s="4" t="inlineStr">
+      <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="S37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="S37" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="T37" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="U37" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗОН</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="X37" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="Y37" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="Z37" s="4" t="n"/>
-      <c r="AA37" s="7" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AB37" s="8" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="Z37" s="7" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="AA37" s="8" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AB37" s="4" t="n"/>
       <c r="AC37" s="4" t="n"/>
       <c r="AD37" s="4" t="n"/>
       <c r="AE37" s="4" t="n"/>
@@ -3115,63 +3135,67 @@
       <c r="M38" s="4" t="n"/>
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n"/>
-      <c r="P38" s="4" t="n"/>
-      <c r="Q38" s="5" t="inlineStr">
+      <c r="P38" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="R38" s="4" t="inlineStr">
+      <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="S38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="U38" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗОН</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="X38" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="Z38" s="4" t="n"/>
-      <c r="AA38" s="7" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AB38" s="8" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="Z38" s="7" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="AA38" s="8" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AB38" s="4" t="n"/>
       <c r="AC38" s="4" t="n"/>
       <c r="AD38" s="4" t="n"/>
       <c r="AE38" s="4" t="n"/>
@@ -3199,63 +3223,67 @@
       <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="n"/>
-      <c r="P39" s="4" t="n"/>
-      <c r="Q39" s="5" t="inlineStr">
+      <c r="P39" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="R39" s="4" t="inlineStr">
+      <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="S39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="T39" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="U39" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗОН</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="X39" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="Y39" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="Z39" s="4" t="n"/>
-      <c r="AA39" s="7" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AB39" s="8" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="Z39" s="7" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="AA39" s="8" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AB39" s="4" t="n"/>
       <c r="AC39" s="4" t="n"/>
       <c r="AD39" s="4" t="n"/>
       <c r="AE39" s="4" t="n"/>
@@ -3323,18 +3351,22 @@
       </c>
       <c r="Z40" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="AA40" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="AB40" s="4" t="n"/>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="AB40" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="AC40" s="7" t="inlineStr">
         <is>
-          <t>ПДГ/ОД</t>
+          <t>ПДГ</t>
         </is>
       </c>
       <c r="AD40" s="8" t="inlineStr">
@@ -3407,18 +3439,22 @@
       </c>
       <c r="Z41" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="AA41" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="AB41" s="4" t="n"/>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="AB41" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="AC41" s="7" t="inlineStr">
         <is>
-          <t>ПДГ/ОД</t>
+          <t>ПДГ</t>
         </is>
       </c>
       <c r="AD41" s="8" t="inlineStr">
@@ -3491,18 +3527,22 @@
       </c>
       <c r="Z42" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="AA42" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="AB42" s="4" t="n"/>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="AB42" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="AC42" s="7" t="inlineStr">
         <is>
-          <t>ПДГ/ОД</t>
+          <t>ПДГ</t>
         </is>
       </c>
       <c r="AD42" s="8" t="inlineStr">
